--- a/entertainment_forms/004_zoom_webinar_registration_form--entertainment_forms.xlsx
+++ b/entertainment_forms/004_zoom_webinar_registration_form--entertainment_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="17" customWidth="1" min="2" max="2"/>
-    <col width="17" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -531,7 +531,7 @@
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -554,7 +554,7 @@
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -577,7 +577,7 @@
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -600,7 +600,7 @@
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -623,7 +623,7 @@
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -646,93 +646,93 @@
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>note</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Date</t>
+          <t>Note</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Note</t>
+          <t>Phone</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>yes_no</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Note</t>
+          <t>Yes/No</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>note2</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Phone</t>
+          <t>Note 2</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -750,12 +750,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_multiple2</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Select Multiple</t>
+          <t>Select Multiple 2</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -768,17 +768,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>time</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>time2</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Select One</t>
+          <t>Time 2</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -796,12 +796,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>email2</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Email 2</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -814,17 +814,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one2</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Select Multiple</t>
+          <t>Select One 2</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -837,251 +837,21 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>note3</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Select One</t>
+          <t>Note 3</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Time</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Note</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Select Multiple</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Note</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>first_name</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>First Name</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Select Multiple</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>last_name</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Last Name</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Select One</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Select Multiple</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Time</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1098,12 +868,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C24"/>
+  <dimension ref="A1:C13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="25" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +901,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'option_1',_'label':_'option_1'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'option_1', 'label': 'Option 1'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1148,12 +918,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'option_2',_'label':_'option_2'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'option_2', 'label': 'Option 2'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1165,12 +935,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'option_3',_'label':_'option_3'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'option_3', 'label': 'Option 3'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1182,12 +952,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'option_4',_'label':_'option_4'}</t>
+          <t>option_4</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'option_4', 'label': 'Option 4'}</t>
+          <t>Option 4</t>
         </is>
       </c>
     </row>
@@ -1199,12 +969,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'option_5',_'label':_'option_5'}</t>
+          <t>option_5</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'option_5', 'label': 'Option 5'}</t>
+          <t>Option 5</t>
         </is>
       </c>
     </row>
@@ -1216,301 +986,114 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'option_6',_'label':_'option_6'}</t>
+          <t>option_6</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'option_6', 'label': 'Option 6'}</t>
+          <t>Option 6</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>select_multiple_choices</t>
+          <t>yes_no_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'option_7',_'label':_'option_7'}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'option_7', 'label': 'Option 7'}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>select_multiple_choices</t>
+          <t>yes_no_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'option_8',_'label':_'option_8'}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'option_8', 'label': 'Option 8'}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>select_multiple_choices</t>
+          <t>select_multiple2_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'option_9',_'label':_'option_9'}</t>
+          <t>option_7</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'option_9', 'label': 'Option 9'}</t>
+          <t>Option 7</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>select_one_choices</t>
+          <t>select_multiple2_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'option_10',_'label':_'option_10'}</t>
+          <t>option_8</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'option_10', 'label': 'Option 10'}</t>
+          <t>Option 8</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>select_one_choices</t>
+          <t>select_one2_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'option_11',_'label':_'option_11'}</t>
+          <t>option_9</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'option_11', 'label': 'Option 11'}</t>
+          <t>Option 9</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>select_multiple_choices</t>
+          <t>select_one2_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'option_12',_'label':_'option_12'}</t>
+          <t>option_10</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'option_12', 'label': 'Option 12'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>select_multiple_choices</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>{'id':_2,_'name':_'option_13',_'label':_'option_13'}</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>{'id': 2, 'name': 'option_13', 'label': 'Option 13'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>select_one_choices</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>select_one_choices</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>select_multiple_choices</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>select_multiple_choices</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>select_multiple_choices</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>{'id':_1,_'name':_'option_14',_'label':_'option_14'}</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>{'id': 1, 'name': 'option_14', 'label': 'Option 14'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>select_multiple_choices</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>{'id':_2,_'name':_'option_15',_'label':_'option_15'}</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>{'id': 2, 'name': 'option_15', 'label': 'Option 15'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>select_one_choices</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>select_one_choices</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>select_multiple_choices</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>select_multiple_choices</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>No</t>
+          <t>Option 10</t>
         </is>
       </c>
     </row>
